--- a/output/laminas_comunales/comunal_i_peringr_median_a_2019_nuble.xlsx
+++ b/output/laminas_comunales/comunal_i_peringr_median_a_2019_nuble.xlsx
@@ -807,7 +807,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -816,11 +816,6 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -828,9 +823,6 @@
           <t>Bulnes</t>
         </is>
       </c>
-      <c r="B2">
-        <v>22.09</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -838,9 +830,6 @@
           <t>Chillán Viejo</t>
         </is>
       </c>
-      <c r="B3">
-        <v>18</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -848,188 +837,131 @@
           <t>Chillán</t>
         </is>
       </c>
-      <c r="B4">
-        <v>18.46</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cobquecura</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>34.49</v>
+          <t>Yungay</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coelemu</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>17.43</v>
+          <t>Quillón</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Coihueco</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>29.01</v>
+          <t>San Carlos</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>El Carmen</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>29.48</v>
+          <t>Treguaco</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ninhue</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>35.54</v>
+          <t>Ranquil</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ñiquén</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>25.88</v>
+          <t>Portezuelo</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pemuco</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>24.8</v>
+          <t>Cobquecura</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pinto</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>26.61</v>
+          <t>Quirihue</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Portezuelo</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>34.65</v>
+          <t>Coelemu</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Quillón</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>24.16</v>
+          <t>Ninhue</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Quirihue</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>27.97</v>
+          <t>Pinto</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ranquil</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>17.98</v>
+          <t>San Ignacio</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>San Carlos</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>24.14</v>
+          <t>Pemuco</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>San Fabián</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>23.99</v>
+          <t>San Nicolás</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>San Ignacio</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>30.41</v>
+          <t>San Fabián</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>San Nicolás</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>23.59</v>
+          <t>Ñiquén</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Treguaco</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>20.76</v>
+          <t>El Carmen</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Yungay</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>16.69</v>
+          <t>Coihueco</t>
+        </is>
       </c>
     </row>
   </sheetData>
